--- a/paper_tables/Table_2_CGCNN_Multi_Property_Evaluation_Metrics.xlsx
+++ b/paper_tables/Table_2_CGCNN_Multi_Property_Evaluation_Metrics.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,8 +468,8 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -478,17 +478,17 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Target Property</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Dataset Partition</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R² Score</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>band_gap</t>
+          <t>Band Gap ($E_g$, eV)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.057</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.075</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>band_gap</t>
+          <t>Band Gap ($E_g$, eV)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.992</v>
+        <v>0.994</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.068</v>
+        <v>0.059</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.092</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>band_gap</t>
+          <t>Band Gap ($E_g$, eV)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.995</v>
+        <v>0.989</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.077</v>
+        <v>0.112</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.096</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>formation_energy</t>
+          <t>Formation Energy ($E_f$, eV/atom)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.997</v>
+        <v>0.993</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.044</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.055</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>formation_energy</t>
+          <t>Formation Energy ($E_f$, eV/atom)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.997</v>
+        <v>0.994</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.038</v>
+        <v>0.062</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.044</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>formation_energy</t>
+          <t>Formation Energy ($E_f$, eV/atom)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.994</v>
+        <v>0.985</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.065</v>
+        <v>0.092</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>energy_hull</t>
+          <t>Energy Above Hull ($E_{\mathrm{hull}}$, eV/atom)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -640,40 +640,40 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.035</v>
+        <v>0.046</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>energy_hull</t>
+          <t>Energy Above Hull ($E_{\mathrm{hull}}$, eV/atom)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.999</v>
+        <v>0.995</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.023</v>
+        <v>0.061</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.031</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>energy_hull</t>
+          <t>Energy Above Hull ($E_{\mathrm{hull}}$, eV/atom)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.039</v>
+        <v>0.055</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.051</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>bulk_modulus</t>
+          <t>Li Adsorption Energy ($E_{\mathrm{ads}}$, eV)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -703,40 +703,40 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.99</v>
+        <v>0.992</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4.977</v>
+        <v>0.068</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>6.145</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>bulk_modulus</t>
+          <t>Li Adsorption Energy ($E_{\mathrm{ads}}$, eV)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.985</v>
+        <v>0.992</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>6.137</v>
+        <v>0.097</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7.802</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>bulk_modulus</t>
+          <t>Li Adsorption Energy ($E_{\mathrm{ads}}$, eV)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.967</v>
+        <v>0.989</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>6.668</v>
+        <v>0.095</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>7.681</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>shear_modulus</t>
+          <t>Bulk Modulus ($K$, GPa)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.997</v>
+        <v>0.998</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2.672</v>
+        <v>2.393</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3.279</v>
+        <v>3.031</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>shear_modulus</t>
+          <t>Bulk Modulus ($K$, GPa)</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2.881</v>
+        <v>2.287</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3.596</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>shear_modulus</t>
+          <t>Bulk Modulus ($K$, GPa)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.966</v>
+        <v>0.987</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.523</v>
+        <v>3.986</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.427</v>
+        <v>4.802</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>young_modulus</t>
+          <t>Shear Modulus ($G$, GPa)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -829,40 +829,40 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.993</v>
+        <v>0.999</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8.577</v>
+        <v>1.762</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10.619</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>young_modulus</t>
+          <t>Shear Modulus ($G$, GPa)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.995</v>
+        <v>0.997</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.692</v>
+        <v>1.733</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7.221</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>young_modulus</t>
+          <t>Shear Modulus ($G$, GPa)</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -871,19 +871,19 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.971</v>
+        <v>0.994</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>7.377</v>
+        <v>1.596</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>10.124</v>
+        <v>1.839</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>E_ads_DFT_eV</t>
+          <t>Young's Modulus ($E$, GPa)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -892,40 +892,40 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.995</v>
+        <v>0.999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.055</v>
+        <v>3.332</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>4.165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>E_ads_DFT_eV</t>
+          <t>Young's Modulus ($E$, GPa)</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.996</v>
+        <v>0.999</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.061</v>
+        <v>2.758</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.077</v>
+        <v>3.331</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>E_ads_DFT_eV</t>
+          <t>Young's Modulus ($E$, GPa)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.992</v>
+        <v>0.99</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.064</v>
+        <v>4.479</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.094</v>
+        <v>5.897</v>
       </c>
     </row>
   </sheetData>
